--- a/교재/엑셀교재v2/024_데이터통합_실습.xlsx
+++ b/교재/엑셀교재v2/024_데이터통합_실습.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F7F2C09-004D-4497-81AA-CADF20556832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5713BEA1-EAD0-4C93-B0A6-3C4BB0A2AA9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24255" yWindow="810" windowWidth="22200" windowHeight="14790" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="1" r:id="rId1"/>
@@ -295,7 +295,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -319,15 +319,18 @@
     <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -557,12 +560,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:4" ht="35.1" customHeight="1">
       <c r="A2" s="1"/>
@@ -571,132 +574,132 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="42" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4" ht="42" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
     </row>
     <row r="5" spans="1:4" ht="42" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" ht="42" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
     </row>
     <row r="7" spans="1:4" ht="42" customHeight="1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" ht="42" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:4" ht="42" customHeight="1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
     </row>
     <row r="10" spans="1:4" ht="42" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
     </row>
     <row r="11" spans="1:4" ht="42" customHeight="1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" spans="1:4" ht="42" customHeight="1">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" ht="42" customHeight="1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:4" ht="42" customHeight="1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
     </row>
     <row r="15" spans="1:4" ht="42" customHeight="1">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:4" ht="42" customHeight="1">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="1:4" ht="42" customHeight="1">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4" ht="42" customHeight="1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" spans="1:4" ht="35.1" customHeight="1">
       <c r="A19" s="1"/>
@@ -711,12 +714,12 @@
       <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:4" ht="35.1" customHeight="1">
       <c r="A22" s="1"/>
@@ -725,20 +728,20 @@
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="1:4" ht="35.1" customHeight="1">
       <c r="A25" s="1"/>
@@ -754,26 +757,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -799,14 +802,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="13"/>
@@ -995,14 +998,14 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="13"/>
@@ -1316,6 +1319,7 @@
       <c r="K27" s="2"/>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <mergeCells count="9">
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A20:I20"/>
@@ -1351,14 +1355,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="13"/>
@@ -1547,14 +1551,14 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="13"/>
@@ -1610,7 +1614,7 @@
       <c r="F11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="9">
         <v>23.333333333333332</v>
       </c>
       <c r="H11" s="8">
@@ -1640,7 +1644,7 @@
       <c r="F12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="9">
         <v>35</v>
       </c>
       <c r="H12" s="8">
@@ -1670,7 +1674,7 @@
       <c r="F13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="9">
         <v>25.666666666666668</v>
       </c>
       <c r="H13" s="8">
@@ -1700,7 +1704,7 @@
       <c r="F14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="9">
         <v>36.666666666666664</v>
       </c>
       <c r="H14" s="8">
@@ -1892,7 +1896,7 @@
       <c r="K27" s="2"/>
     </row>
   </sheetData>
-  <dataConsolidate function="average" leftLabels="1" topLabels="1">
+  <dataConsolidate function="average" topLabels="1">
     <dataRefs count="3">
       <dataRef ref="A2:D6" sheet="평균통합_정답"/>
       <dataRef ref="F2:I6" sheet="평균통합_정답"/>
@@ -1934,14 +1938,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="13"/>
@@ -2130,14 +2134,14 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="13"/>
@@ -2449,17 +2453,24 @@
       <c r="K27" s="2"/>
     </row>
   </sheetData>
+  <dataConsolidate leftLabels="1" topLabels="1">
+    <dataRefs count="3">
+      <dataRef ref="A2:D6" sheet="분석작업-2"/>
+      <dataRef ref="F2:I6" sheet="분석작업-2"/>
+      <dataRef ref="A10:D14" sheet="분석작업-2"/>
+    </dataRefs>
+  </dataConsolidate>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="A17:I17"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2485,14 +2496,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="13"/>
@@ -2681,14 +2692,14 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="14" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="13"/>
@@ -2744,7 +2755,7 @@
       <c r="F11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="15">
         <v>216</v>
       </c>
       <c r="H11" s="8">
@@ -2774,7 +2785,7 @@
       <c r="F12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="15">
         <v>138</v>
       </c>
       <c r="H12" s="8">
@@ -3020,16 +3031,16 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="A17:I17"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
